--- a/docs/测试材料/01-正式提交材料/最终提交/bug_list.xlsx
+++ b/docs/测试材料/01-正式提交材料/最终提交/bug_list.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D55611C-A062-4DED-8E44-FD72F41DF168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2136" yWindow="2124" windowWidth="20184" windowHeight="10296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Bug確認">[1]OTHER!$D$2:$D$10</definedName>
@@ -26,93 +28,492 @@
     <definedName name="影響度">[1]OTHER!$H$2:$H$6</definedName>
     <definedName name="再現頻度">[1]OTHER!$F$2:$F$8</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+  <si>
+    <t>重要度</t>
+    <rPh sb="0" eb="3">
+      <t>ｼﾞｭｳﾖｳﾄﾞ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答者</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答日</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <rPh sb="0" eb="2">
+      <t>ﾊﾞンｺﾞウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生模块</t>
+    <rPh sb="0" eb="2">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题点</t>
+    <rPh sb="0" eb="2">
+      <t>シテキｼﾞコウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应测试项目</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウカコウモク</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试环境，测试对象的版本</t>
+    <rPh sb="6" eb="8">
+      <t>ﾌﾞッケン</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bug原因</t>
+    <rPh sb="0" eb="2">
+      <t>ｹﾞンイン</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bug一览表</t>
+    <rPh sb="0" eb="3">
+      <t>ﾀﾞｲｻﾝｼｬ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ﾋｮｳｶﾃｷｼｭﾂショウｶﾞイ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 问题总数：</t>
+    <rPh sb="1" eb="3">
+      <t>モンﾀﾞイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试G记入</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キニュウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发G记入</t>
+    <rPh sb="3" eb="5">
+      <t>キニュウイｶﾞイﾊﾞアイキニュウフヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试G记入</t>
+    <rPh sb="3" eb="5">
+      <t>キニュウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bug
+状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告日</t>
+    <rPh sb="0" eb="2">
+      <t>テキシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ﾋﾞ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>再现步骤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>再现频度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改处理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试G
+确认者</t>
+    <rPh sb="4" eb="6">
+      <t>ｶｸﾆﾝ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ｼｬ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试G
+确认日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>説明：
+ 1. 如果是开发人员和测试人员同时发现的同一件bug，作为一件bug登记。
+ 2. 下表中，红色部分，必须要记入。
+ 3. 测试期间，测试组应该每天提出bug表，开发组应当天或者隔天进行回复。</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ﾄﾞウｼﾞ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ｼﾞュウフク</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>アカイロ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>ツﾊﾞアイナイヨウキニュウヒョウカキカンヒョウカマイニチショウｶﾞイイチランヒョウテイシュツカイハツモンﾀﾞイタイニチニチｺﾞトカイトウショウｶﾞイイチランヒョウヘンシンヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发G
+Bug确认</t>
+    <rPh sb="7" eb="9">
+      <t>ｶｸﾆﾝ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备考</t>
+    <rPh sb="0" eb="2">
+      <t>ﾋﾞｺｳ</t>
+    </rPh>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>李艺涵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/6//12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>环境/认证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顾客下单模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>期待结果：
+输入不合法电话号应拒绝创建地址信息
+问题点：
+仅拒接除数字以外的其他字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生条件：
+在管理地址页面创建新地址时，填充电话号时
+步骤：
+填充不符合中国大陆电话号规范格式的字符串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次</t>
+  </si>
+  <si>
+    <t>FT-006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT-016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FT-020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生条件：
+全新 Python 3.10+ 虚拟环境，按原始 requirements.txt 安装
+步骤：
+1. 创建干净虚拟环境
+2. 启动后端服务
+3. 调用 POST /api/auth/register 注册任意账号
+4. 调用 POST /api/auth/login 登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期待结果：
+从干净环境按 requirements.txt 安装依赖后，注册和登录功能正常可用
+问题点：
+requirements.txt 中 bcrypt 未固定版本，最新 bcrypt 4.x 的 API 变更导致 passlib 的 bcrypt 后端无法正常工作，注册和登录均抛出异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期待结果：
+输入栏输入0或负数应拒绝下单
+问题点：
+订单数量为NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生条件：
+在指定商家菜品界面添加菜品后
+步骤：
+购物车内不使用加减交互键，使用输入栏输入零或负数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改善事项</t>
+  </si>
+  <si>
+    <t>bcrypt 4.x 版本中移除了旧版 API（__about__ 模块），passlib 1.7.4 的 bcrypt 后端依赖该 API 导致 ImportError/ValueError。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未使用正则表达式匹配输入字符串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未考虑输入校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加中国大陆手机号的正则表达式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 requirements.txt 中固定 bcrypt==3.2.2，同时添加 passlib[bcrypt]==1.7.4 显式声明；后续可考虑迁移至 passlib 替代方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加输入校验，输入必须为正整数，否则从购物车清除该菜品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后端开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows / FastAPI TestClient / SQLite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复后，FT-006回归通过。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复后，FT-016回归通过。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复后，FT-020回归通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="12"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="12"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="12"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="12"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,7 +537,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -222,226 +623,118 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -452,11 +745,11 @@
     <dxf>
       <font>
         <condense val="0"/>
+        <extend val="0"/>
         <color indexed="10"/>
-        <extend val="0"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="none">
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
@@ -477,12 +770,24 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFFFF"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Cover"/>
@@ -641,7 +946,9 @@
           <cell r="G6" t="str">
             <v>確認評価待ち</v>
           </cell>
-          <cell r="I6" t="str"/>
+          <cell r="I6" t="str">
+            <v/>
+          </cell>
           <cell r="J6" t="str">
             <v>限界値</v>
           </cell>
@@ -659,7 +966,9 @@
           <cell r="G7" t="str">
             <v>確認評価実行中</v>
           </cell>
-          <cell r="I7" t="str"/>
+          <cell r="I7" t="str">
+            <v/>
+          </cell>
           <cell r="J7" t="str">
             <v>同時アクセス</v>
           </cell>
@@ -677,7 +986,9 @@
           <cell r="G8" t="str">
             <v>完了(確認評価済み)</v>
           </cell>
-          <cell r="I8" t="str"/>
+          <cell r="I8" t="str">
+            <v/>
+          </cell>
           <cell r="J8" t="str">
             <v>ファイル関連</v>
           </cell>
@@ -695,7 +1006,9 @@
           <cell r="G9" t="str">
             <v>完了(確認評価不要)</v>
           </cell>
-          <cell r="I9" t="str"/>
+          <cell r="I9" t="str">
+            <v/>
+          </cell>
           <cell r="J9" t="str">
             <v>メッセージ</v>
           </cell>
@@ -710,127 +1023,191 @@
           <cell r="G10" t="str">
             <v>廃棄</v>
           </cell>
-          <cell r="I10" t="str"/>
+          <cell r="I10" t="str">
+            <v/>
+          </cell>
           <cell r="J10" t="str">
             <v>組み合わせ</v>
           </cell>
         </row>
         <row r="11">
-          <cell r="I11" t="str"/>
+          <cell r="I11" t="str">
+            <v/>
+          </cell>
           <cell r="J11" t="str">
             <v>検索ソート</v>
           </cell>
         </row>
         <row r="12">
-          <cell r="I12" t="str"/>
+          <cell r="I12" t="str">
+            <v/>
+          </cell>
           <cell r="J12" t="str">
             <v>特殊文字</v>
           </cell>
         </row>
         <row r="13">
-          <cell r="I13" t="str"/>
+          <cell r="I13" t="str">
+            <v/>
+          </cell>
           <cell r="J13" t="str">
             <v>削除関係</v>
           </cell>
         </row>
         <row r="14">
-          <cell r="I14" t="str"/>
+          <cell r="I14" t="str">
+            <v/>
+          </cell>
           <cell r="J14" t="str">
             <v>データ計算</v>
           </cell>
         </row>
         <row r="15">
-          <cell r="I15" t="str"/>
+          <cell r="I15" t="str">
+            <v/>
+          </cell>
           <cell r="J15" t="str">
             <v>ヘルプ・マニュアル</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="I16" t="str"/>
+          <cell r="I16" t="str">
+            <v/>
+          </cell>
           <cell r="J16" t="str">
             <v>ページ制御</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="I17" t="str"/>
+          <cell r="I17" t="str">
+            <v/>
+          </cell>
           <cell r="J17" t="str">
             <v>ログ</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="I18" t="str"/>
+          <cell r="I18" t="str">
+            <v/>
+          </cell>
           <cell r="J18" t="str">
             <v>キーボート操作</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="I19" t="str"/>
+          <cell r="I19" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="20">
-          <cell r="I20" t="str"/>
+          <cell r="I20" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="21">
-          <cell r="I21" t="str"/>
+          <cell r="I21" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="22">
-          <cell r="I22" t="str"/>
+          <cell r="I22" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="23">
-          <cell r="I23" t="str"/>
+          <cell r="I23" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="24">
-          <cell r="I24" t="str"/>
+          <cell r="I24" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="25">
-          <cell r="I25" t="str"/>
+          <cell r="I25" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="26">
-          <cell r="I26" t="str"/>
+          <cell r="I26" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="27">
-          <cell r="I27" t="str"/>
+          <cell r="I27" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="28">
-          <cell r="I28" t="str"/>
+          <cell r="I28" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="29">
-          <cell r="I29" t="str"/>
+          <cell r="I29" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="30">
-          <cell r="I30" t="str"/>
+          <cell r="I30" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="31">
-          <cell r="I31" t="str"/>
+          <cell r="I31" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="32">
-          <cell r="I32" t="str"/>
+          <cell r="I32" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="33">
-          <cell r="I33" t="str"/>
+          <cell r="I33" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="34">
-          <cell r="I34" t="str"/>
+          <cell r="I34" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="35">
-          <cell r="I35" t="str"/>
+          <cell r="I35" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="36">
-          <cell r="I36" t="str"/>
+          <cell r="I36" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="37">
-          <cell r="I37" t="str"/>
+          <cell r="I37" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="38">
-          <cell r="I38" t="str"/>
+          <cell r="I38" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="39">
-          <cell r="I39" t="str"/>
+          <cell r="I39" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="40">
-          <cell r="I40" t="str"/>
+          <cell r="I40" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="41">
-          <cell r="I41" t="str"/>
+          <cell r="I41" t="str">
+            <v/>
+          </cell>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -1158,710 +1535,425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5.7265625" customWidth="1" style="2" min="1" max="2"/>
-    <col width="9" customWidth="1" style="2" min="3" max="16384"/>
+    <col min="1" max="2" width="5.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="2"/>
+    <col min="18" max="18" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="n"/>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
-      <c r="H1" s="32" t="n"/>
-      <c r="I1" s="32" t="n"/>
-      <c r="J1" s="32" t="n"/>
-      <c r="K1" s="32" t="n"/>
-      <c r="L1" s="32" t="n"/>
-      <c r="M1" s="32" t="n"/>
-      <c r="N1" s="32" t="n"/>
-      <c r="O1" s="32" t="n"/>
-      <c r="P1" s="32" t="n"/>
-      <c r="Q1" s="32" t="n"/>
-      <c r="R1" s="32" t="n"/>
-      <c r="S1" s="33" t="n"/>
+    <row r="1" spans="1:19">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>bug一览表</t>
-        </is>
-      </c>
-      <c r="B2" s="32" t="n"/>
-      <c r="C2" s="32" t="n"/>
-      <c r="D2" s="32" t="n"/>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 问题总数：</t>
-        </is>
-      </c>
-      <c r="F2" s="32" t="n"/>
+    <row r="2" spans="1:19" ht="15.6">
+      <c r="A2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="22"/>
       <c r="G2" s="3">
-        <f>COUNTA(B6:B12)</f>
-        <v/>
-      </c>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="20" t="n"/>
-      <c r="K2" s="20" t="n"/>
-      <c r="L2" s="20" t="n"/>
-      <c r="M2" s="20" t="n"/>
-      <c r="N2" s="20" t="n"/>
-      <c r="O2" s="20" t="n"/>
-      <c r="P2" s="20" t="n"/>
-      <c r="Q2" s="20" t="n"/>
-      <c r="R2" s="20" t="n"/>
-      <c r="S2" s="5" t="n"/>
+        <f>COUNTIF(A6:A912,"*")</f>
+        <v>3</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="5"/>
     </row>
-    <row r="3" ht="77.25" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>説明：
- 1. 如果是开发人员和测试人员同时发现的同一件bug，作为一件bug登记。
- 2. 下表中，红色部分，必须要记入。
- 3. 测试期间，测试组应该每天提出bug表，开发组应当天或者隔天进行回复。</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="n"/>
-      <c r="C3" s="32" t="n"/>
-      <c r="D3" s="32" t="n"/>
-      <c r="E3" s="32" t="n"/>
-      <c r="F3" s="32" t="n"/>
-      <c r="G3" s="32" t="n"/>
-      <c r="H3" s="32" t="n"/>
-      <c r="I3" s="32" t="n"/>
-      <c r="J3" s="32" t="n"/>
-      <c r="K3" s="32" t="n"/>
-      <c r="L3" s="32" t="n"/>
-      <c r="M3" s="32" t="n"/>
-      <c r="N3" s="32" t="n"/>
-      <c r="O3" s="32" t="n"/>
-      <c r="P3" s="32" t="n"/>
-      <c r="Q3" s="32" t="n"/>
-      <c r="R3" s="32" t="n"/>
-      <c r="S3" s="33" t="n"/>
+    <row r="3" spans="1:19" ht="77.25" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="25"/>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>测试G记入</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="32" t="n"/>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="32" t="n"/>
-      <c r="J4" s="32" t="n"/>
-      <c r="K4" s="32" t="n"/>
-      <c r="L4" s="35" t="inlineStr">
-        <is>
-          <t>开发G记入</t>
-        </is>
-      </c>
-      <c r="M4" s="32" t="n"/>
-      <c r="N4" s="32" t="n"/>
-      <c r="O4" s="32" t="n"/>
-      <c r="P4" s="33" t="n"/>
-      <c r="Q4" s="26" t="inlineStr">
-        <is>
-          <t>测试G记入</t>
-        </is>
-      </c>
-      <c r="R4" s="32" t="n"/>
-      <c r="S4" s="6" t="n"/>
+    <row r="4" spans="1:19" ht="15.6">
+      <c r="A4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="R4" s="27"/>
+      <c r="S4" s="6"/>
     </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>bug
-状态</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>报告者</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>报告日</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>发生模块</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>重要度</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>问题点</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>再现步骤</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>再现频度</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>对应测试项目</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>测试环境，测试对象的版本</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>开发G
-Bug确认</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>bug原因</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>修改处理</t>
-        </is>
-      </c>
-      <c r="O5" s="36" t="inlineStr">
-        <is>
-          <t>回答者</t>
-        </is>
-      </c>
-      <c r="P5" s="36" t="inlineStr">
-        <is>
-          <t>回答日</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>测试G
-确认者</t>
-        </is>
-      </c>
-      <c r="R5" s="37" t="inlineStr">
-        <is>
-          <t>测试G
-确认日</t>
-        </is>
-      </c>
-      <c r="S5" s="12" t="inlineStr">
-        <is>
-          <t>备考</t>
-        </is>
+    <row r="5" spans="1:19" ht="48">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="38" t="inlineStr">
-        <is>
-          <t>已关闭</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>李艺涵</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E6" s="39" t="inlineStr">
-        <is>
-          <t>并发/骑手</t>
-        </is>
-      </c>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
-        <is>
-          <t>期待结果：
-并发抢单时，多个骑手同时请求同一订单，仅一个骑手抢单成功，返回 200；其余骑手返回 409 Conflict。
-问题点：
-当前实现未使用数据库行锁或原子条件更新，在并发场景下可能出现双骑手同时抢单成功（竞态条件）。</t>
-        </is>
-      </c>
-      <c r="H6" s="40" t="inlineStr">
-        <is>
-          <t>发生条件：
-1 个待配送订单 + 2 个空闲骑手账号
-步骤：
-1. 使用顾客账号下单，商家接单后进入待配送状态
-2. 使用 asyncio.gather() 并发调用两个骑手的抢单接口
-3. 检查两个请求的返回结果及订单的骑手 ID</t>
-        </is>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>必现（并发条件下）</t>
-        </is>
-      </c>
-      <c r="J6" s="39" t="inlineStr">
-        <is>
-          <t>FT-011</t>
-        </is>
-      </c>
-      <c r="K6" s="39" t="inlineStr">
-        <is>
-          <t>Windows / FastAPI TestClient / SQLite</t>
-        </is>
-      </c>
-      <c r="L6" s="41" t="inlineStr">
-        <is>
-          <t>确认为缺陷</t>
-        </is>
-      </c>
-      <c r="M6" s="42" t="inlineStr">
-        <is>
-          <t>抢单逻辑未使用数据库原子操作（如 UPDATE ... WHERE status=:old_status AND courier_id IS NULL）或 SELECT ... FOR UPDATE 行锁，导致并发请求同时读到旧状态并各自写入。</t>
-        </is>
-      </c>
-      <c r="N6" s="42" t="inlineStr">
-        <is>
-          <t>采用 SQLAlchemy 原子条件更新：UPDATE orders SET courier_id=:cid, status='delivering' WHERE id=:oid AND status='pending_delivery' AND courier_id IS NULL，通过 rowcount 判断是否抢单成功。</t>
-        </is>
-      </c>
-      <c r="O6" s="42" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="P6" s="42" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="Q6" s="40" t="inlineStr">
-        <is>
-          <t>李艺涵</t>
-        </is>
-      </c>
-      <c r="R6" s="40" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="S6" s="40" t="inlineStr">
-        <is>
-          <t>修复后 FT-011 回归通过。commit 956d9b0</t>
-        </is>
+    <row r="6" spans="1:19" ht="118.8">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="14">
+        <v>46183</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="P6" s="17">
+        <v>46185</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="32">
+        <v>46190</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="38" t="inlineStr">
-        <is>
-          <t>已关闭</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="inlineStr">
-        <is>
-          <t>李艺涵</t>
-        </is>
-      </c>
-      <c r="D7" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="E7" s="39" t="inlineStr">
-        <is>
-          <t>环境/认证</t>
-        </is>
-      </c>
-      <c r="F7" s="40" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G7" s="40" t="inlineStr">
-        <is>
-          <t>期待结果：
-从干净环境按 requirements.txt 安装依赖后，注册和登录功能正常可用，返回 JWT Token。
-问题点：
-requirements.txt 中 bcrypt 未固定版本，最新 bcrypt 4.x 的 API 变更导致 passlib 的 bcrypt 后端无法正常工作，注册和登录均抛出异常。</t>
-        </is>
-      </c>
-      <c r="H7" s="40" t="inlineStr">
-        <is>
-          <t>发生条件：
-全新 Python 3.10+ 虚拟环境，按原始 requirements.txt 安装
-步骤：
-1. 创建干净虚拟环境，pip install -r requirements.txt
-2. 启动后端服务
-3. 调用 POST /api/auth/register 注册任意账号
-4. 调用 POST /api/auth/login 登录</t>
-        </is>
-      </c>
-      <c r="I7" s="39" t="inlineStr">
-        <is>
-          <t>必现（使用 bcrypt&gt;=4.0 时）</t>
-        </is>
-      </c>
-      <c r="J7" s="39" t="inlineStr">
-        <is>
-          <t>FT-015</t>
-        </is>
-      </c>
-      <c r="K7" s="39" t="inlineStr">
-        <is>
-          <t>Windows / Python 3.10+ / 干净虚拟环境</t>
-        </is>
-      </c>
-      <c r="L7" s="41" t="inlineStr">
-        <is>
-          <t>确认为缺陷</t>
-        </is>
-      </c>
-      <c r="M7" s="42" t="inlineStr">
-        <is>
-          <t>bcrypt 4.x 版本中移除了旧版 API（__about__ 模块），passlib 1.7.4 的 bcrypt 后端依赖该 API 导致 ImportError/ValueError。</t>
-        </is>
-      </c>
-      <c r="N7" s="42" t="inlineStr">
-        <is>
-          <t>在 requirements.txt 中固定 bcrypt==3.2.2，同时添加 passlib[bcrypt]==1.7.4 显式声明；后续可考虑迁移至 passlib 替代方案。</t>
-        </is>
-      </c>
-      <c r="O7" s="42" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="P7" s="42" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="Q7" s="40" t="inlineStr">
-        <is>
-          <t>李艺涵</t>
-        </is>
-      </c>
-      <c r="R7" s="40" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="S7" s="40" t="inlineStr">
-        <is>
-          <t>修复后 FT-015 回归通过。commit 956d9b0</t>
-        </is>
+    <row r="7" spans="1:19" ht="123.6" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="17">
+        <v>46189</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="32">
+        <v>46190</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="46" t="n"/>
-      <c r="G8" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待结果：
-问题点：
-</t>
-        </is>
-      </c>
-      <c r="H8" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发生条件：
-步骤：
-</t>
-        </is>
-      </c>
-      <c r="I8" s="45" t="n"/>
-      <c r="J8" s="45" t="n"/>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="47" t="n"/>
-      <c r="M8" s="48" t="n"/>
-      <c r="N8" s="48" t="n"/>
-      <c r="O8" s="48" t="n"/>
-      <c r="P8" s="48" t="n"/>
-      <c r="Q8" s="46" t="n"/>
-      <c r="R8" s="46" t="n"/>
-      <c r="S8" s="46" t="n"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="45" t="n"/>
-      <c r="D9" s="45" t="n"/>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待结果：
-问题点：
-</t>
-        </is>
-      </c>
-      <c r="H9" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发生条件：
-步骤：
-</t>
-        </is>
-      </c>
-      <c r="I9" s="45" t="n"/>
-      <c r="J9" s="45" t="n"/>
-      <c r="K9" s="45" t="n"/>
-      <c r="L9" s="47" t="n"/>
-      <c r="M9" s="48" t="n"/>
-      <c r="N9" s="48" t="n"/>
-      <c r="O9" s="48" t="n"/>
-      <c r="P9" s="48" t="n"/>
-      <c r="Q9" s="46" t="n"/>
-      <c r="R9" s="46" t="n"/>
-      <c r="S9" s="46" t="n"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="43" t="n">
+    <row r="8" spans="1:19" ht="118.8">
+      <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="45" t="n"/>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待结果：
-问题点：
-</t>
-        </is>
-      </c>
-      <c r="H10" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发生条件：
-步骤：
-</t>
-        </is>
-      </c>
-      <c r="I10" s="45" t="n"/>
-      <c r="J10" s="45" t="n"/>
-      <c r="K10" s="45" t="n"/>
-      <c r="L10" s="47" t="n"/>
-      <c r="M10" s="48" t="n"/>
-      <c r="N10" s="48" t="n"/>
-      <c r="O10" s="48" t="n"/>
-      <c r="P10" s="48" t="n"/>
-      <c r="Q10" s="46" t="n"/>
-      <c r="R10" s="46" t="n"/>
-      <c r="S10" s="46" t="n"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待结果：
-问题点：
-</t>
-        </is>
-      </c>
-      <c r="H11" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发生条件：
-步骤：
-</t>
-        </is>
-      </c>
-      <c r="I11" s="45" t="n"/>
-      <c r="J11" s="45" t="n"/>
-      <c r="K11" s="45" t="n"/>
-      <c r="L11" s="47" t="n"/>
-      <c r="M11" s="48" t="n"/>
-      <c r="N11" s="48" t="n"/>
-      <c r="O11" s="48" t="n"/>
-      <c r="P11" s="48" t="n"/>
-      <c r="Q11" s="46" t="n"/>
-      <c r="R11" s="46" t="n"/>
-      <c r="S11" s="46" t="n"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">期待结果：
-问题点：
-</t>
-        </is>
-      </c>
-      <c r="H12" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发生条件：
-步骤：
-</t>
-        </is>
-      </c>
-      <c r="I12" s="45" t="n"/>
-      <c r="J12" s="45" t="n"/>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="47" t="n"/>
-      <c r="M12" s="48" t="n"/>
-      <c r="N12" s="48" t="n"/>
-      <c r="O12" s="48" t="n"/>
-      <c r="P12" s="48" t="n"/>
-      <c r="Q12" s="46" t="n"/>
-      <c r="R12" s="46" t="n"/>
-      <c r="S12" s="46" t="n"/>
+      <c r="B8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="14">
+        <v>46185</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="17">
+        <v>46185</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="32">
+        <v>46190</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:K4"/>
     <mergeCell ref="L4:P4"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="Q4:R4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6:L12 C7:O12 M6:O6 Q6:R12">
-    <cfRule type="expression" priority="8" dxfId="0" stopIfTrue="1">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="M6:O6 C6:L8 Q6:R8 C7:P8">
+    <cfRule type="expression" dxfId="3" priority="8" stopIfTrue="1">
       <formula>IF($A6&lt;&gt;"",IF(C6="",TRUE,FALSE),FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M12 M9:P10 M12:P12 N7:N12 O6:P12">
-    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+  <conditionalFormatting sqref="N7:N8 M6:M8 O6:P8">
+    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
       <formula>IF($L6="バグ",IF(M6="",TRUE,FALSE),FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>IF($L6="Yes",FALSE,IF(M6&lt;&gt;"",TRUE,FALSE))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N12">
-    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="1">
-      <formula>IF($A7&lt;&gt;"",IF(N7="",TRUE,FALSE),FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
-      <formula>IF($A9&lt;&gt;"",IF(N9="",TRUE,FALSE),FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
-      <formula>IF($A11&lt;&gt;"",IF(N11="",TRUE,FALSE),FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="P6">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>IF($A6&lt;&gt;"",IF(P6="",TRUE,FALSE),FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P12">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>IF($A7&lt;&gt;"",IF(P7="",TRUE,FALSE),FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="Q6:Q12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q6:Q8" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>リーダ</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:H12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:H8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>影響度</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B8" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"ACTIVE,CLOSED"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L8" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"改善事项,bug,不是问题"</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I6:I8" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"每次,偶尔,一次"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F8" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"高,中,底"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>